--- a/checklist_forms/045_distributed_team_onboarding_automation_checklist--checklist_forms.xlsx
+++ b/checklist_forms/045_distributed_team_onboarding_automation_checklist--checklist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'ready',_'value':_'ready'}</t>
+          <t>ready</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Ready', 'value': 'Ready'}</t>
+          <t>Ready</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'not_ready',_'value':_'not_ready'}</t>
+          <t>not_ready</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Not Ready', 'value': 'Not Ready'}</t>
+          <t>Not Ready</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'team_lead_introduction',_'value':_'team_lead_introduction'}</t>
+          <t>team_lead_introduction</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Team Lead Introduction', 'value': 'Team Lead Introduction'}</t>
+          <t>Team Lead Introduction</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'project_overview',_'value':_'project_overview'}</t>
+          <t>project_overview</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Project Overview', 'value': 'Project Overview'}</t>
+          <t>Project Overview</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'team_members_introduction',_'value':_'team_members_introduction'}</t>
+          <t>team_members_introduction</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Team Members Introduction', 'value': 'Team Members Introduction'}</t>
+          <t>Team Members Introduction</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'first_week_tasks',_'value':_'first_week_tasks'}</t>
+          <t>first_week_tasks</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'First Week Tasks', 'value': 'First Week Tasks'}</t>
+          <t>First Week Tasks</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'access_and_setup',_'value':_'access_and_setup'}</t>
+          <t>access_and_setup</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Access and Setup', 'value': 'Access and Setup'}</t>
+          <t>Access and Setup</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'company_email',_'value':_'company_email'}</t>
+          <t>company_email</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Company Email', 'value': 'Company Email'}</t>
+          <t>Company Email</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'company_phone',_'value':_'company_phone'}</t>
+          <t>company_phone</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Company Phone', 'value': 'Company Phone'}</t>
+          <t>Company Phone</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'team_lead',_'value':_'team_lead'}</t>
+          <t>team_lead</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Team Lead', 'value': 'Team Lead'}</t>
+          <t>Team Lead</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'project_manager',_'value':_'project_manager'}</t>
+          <t>project_manager</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Project Manager', 'value': 'Project Manager'}</t>
+          <t>Project Manager</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'slack',_'value':_'slack'}</t>
+          <t>slack</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Slack', 'value': 'Slack'}</t>
+          <t>Slack</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'skype',_'value':_'skype'}</t>
+          <t>skype</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Skype', 'value': 'Skype'}</t>
+          <t>Skype</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'zoom',_'value':_'zoom'}</t>
+          <t>zoom</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Zoom', 'value': 'Zoom'}</t>
+          <t>Zoom</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'team_lead',_'value':_'team_lead'}</t>
+          <t>team_lead</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Team Lead', 'value': 'Team Lead'}</t>
+          <t>Team Lead</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'project_description',_'value':_'project_description'}</t>
+          <t>project_description</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Project Description', 'value': 'Project Description'}</t>
+          <t>Project Description</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'project_goals',_'value':_'project_goals'}</t>
+          <t>project_goals</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Project Goals', 'value': 'Project Goals'}</t>
+          <t>Project Goals</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'team_project',_'value':_'team_project'}</t>
+          <t>team_project</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Team Project', 'value': 'Team Project'}</t>
+          <t>Team Project</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'project_status',_'value':_'project_status'}</t>
+          <t>project_status</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Project Status', 'value': 'Project Status'}</t>
+          <t>Project Status</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'team_lead',_'value':_'team_lead'}</t>
+          <t>team_lead</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Team Lead', 'value': 'Team Lead'}</t>
+          <t>Team Lead</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'team_members',_'value':_'team_members'}</t>
+          <t>team_members</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Team Members', 'value': 'Team Members'}</t>
+          <t>Team Members</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'team_project_leads',_'value':_'team_project_leads'}</t>
+          <t>team_project_leads</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Team Project Leads', 'value': 'Team Project Leads'}</t>
+          <t>Team Project Leads</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'project_manager',_'value':_'project_manager'}</t>
+          <t>project_manager</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Project Manager', 'value': 'Project Manager'}</t>
+          <t>Project Manager</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'task_1',_'value':_'task_1'}</t>
+          <t>task_1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Task 1', 'value': 'Task 1'}</t>
+          <t>Task 1</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'task_2',_'value':_'task_2'}</t>
+          <t>task_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Task 2', 'value': 'Task 2'}</t>
+          <t>Task 2</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'task_3',_'value':_'task_3'}</t>
+          <t>task_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Task 3', 'value': 'Task 3'}</t>
+          <t>Task 3</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'task_4',_'value':_'task_4'}</t>
+          <t>task_4</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Task 4', 'value': 'Task 4'}</t>
+          <t>Task 4</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'task_5',_'value':_'task_5'}</t>
+          <t>task_5</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Task 5', 'value': 'Task 5'}</t>
+          <t>Task 5</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'task_6',_'value':_'task_6'}</t>
+          <t>task_6</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Task 6', 'value': 'Task 6'}</t>
+          <t>Task 6</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'task_7',_'value':_'task_7'}</t>
+          <t>task_7</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Task 7', 'value': 'Task 7'}</t>
+          <t>Task 7</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'task_8',_'value':_'task_8'}</t>
+          <t>task_8</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Task 8', 'value': 'Task 8'}</t>
+          <t>Task 8</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'task_9',_'value':_'task_9'}</t>
+          <t>task_9</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Task 9', 'value': 'Task 9'}</t>
+          <t>Task 9</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'task_10',_'value':_'task_10'}</t>
+          <t>task_10</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'Task 10', 'value': 'Task 10'}</t>
+          <t>Task 10</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'onboarding_completed',_'value':_'onboarding_completed'}</t>
+          <t>onboarding_completed</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'Onboarding Completed', 'value': 'Onboarding Completed'}</t>
+          <t>Onboarding Completed</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'not_completed',_'value':_'not_completed'}</t>
+          <t>not_completed</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'Not Completed', 'value': 'Not Completed'}</t>
+          <t>Not Completed</t>
         </is>
       </c>
     </row>
